--- a/Excel.temp/GOPH 457 MIDTERM 1.xlsx
+++ b/Excel.temp/GOPH 457 MIDTERM 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bddd1913fb6f10a7/Documents/SCHOOL/GOPH 457 L01 - (Winter 2025) - Physical Properties of Minerals^J Soils and Rock - 2132025 - 835 AM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="933" documentId="8_{A6E124A9-3F37-4D6B-94E3-22EA175D76B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{295E2DCC-08E8-4B65-9760-2B16B442A4D1}"/>
+  <xr:revisionPtr revIDLastSave="1170" documentId="8_{A6E124A9-3F37-4D6B-94E3-22EA175D76B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68DE15F4-68DF-4525-9993-4E7F14968AF1}"/>
   <bookViews>
-    <workbookView xWindow="36765" yWindow="0" windowWidth="12240" windowHeight="16305" activeTab="1" xr2:uid="{324697F0-F716-4973-9DEE-7915F077F450}"/>
+    <workbookView xWindow="36765" yWindow="0" windowWidth="12660" windowHeight="16305" activeTab="2" xr2:uid="{324697F0-F716-4973-9DEE-7915F077F450}"/>
   </bookViews>
   <sheets>
     <sheet name="Q1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="153">
   <si>
     <t>r = 2.58 ± 0.05 cm</t>
   </si>
@@ -274,9 +274,6 @@
     <t>Pa (roh air)</t>
   </si>
   <si>
-    <t>Pa (roh water)</t>
-  </si>
-  <si>
     <t>Falling head calculation</t>
   </si>
   <si>
@@ -316,19 +313,190 @@
     <t>Constant head calculation</t>
   </si>
   <si>
-    <t>Volume Calculation: Geometric Method</t>
-  </si>
-  <si>
-    <t>Volume Calculation: Archimedes Method</t>
-  </si>
-  <si>
     <t>Msub</t>
   </si>
   <si>
-    <t>The relative error obtained from implementing the Archimedes method was overall more reliable in estimating our volumes because the value obtained showed a lower relative error.</t>
-  </si>
-  <si>
-    <t>Hydraulic conductivity is defined as the measure of the ease through which fluids moves throug a permeable body for example soil. Permeability is d</t>
+    <t>Q3.</t>
+  </si>
+  <si>
+    <t>Hydraulic conductivity measues how easily fluids flow through a porous material within a hydraulic gradient. Permeability is a material property that describes the ability of fluids to move through materials, independent of the fluid type. Hydraulic conductivity is measured in m/s and permeability is measured in m^2 . Hy draulic conductivity depends on the fluid properties meanwhile permeability depends on the intrinsic property of the material the fluids are flowing through.</t>
+  </si>
+  <si>
+    <t>Comparing the results from b and c to see if they agree within experimantal error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">While calculating the value of constant head in part b we obtained </t>
+  </si>
+  <si>
+    <t>(i) Volume Calculation: Geometric Method</t>
+  </si>
+  <si>
+    <t>(ii) Volume Calculation: Archimedes Method</t>
+  </si>
+  <si>
+    <t>The method that involved volume calculation by specimen dimensions produced a higher relative error at (0.02) .Yes the volume estimates agree with the experimental error. The relative error obtained from implementing the Archimedes method was overall more reliable in estimating our volumes because the value obtained showed a lower relative error based on error estimates.</t>
+  </si>
+  <si>
+    <t>Silt sand</t>
+  </si>
+  <si>
+    <t>Lacustrine Clay</t>
+  </si>
+  <si>
+    <t>Well-graded gravel</t>
+  </si>
+  <si>
+    <t>Thickness (m)</t>
+  </si>
+  <si>
+    <t>K (m/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. </t>
+  </si>
+  <si>
+    <t>Hydraulic Gradient Calculation</t>
+  </si>
+  <si>
+    <t>Layers</t>
+  </si>
+  <si>
+    <t>Excavation Depth</t>
+  </si>
+  <si>
+    <t>SPDBE</t>
+  </si>
+  <si>
+    <t>Natural water Tbl</t>
+  </si>
+  <si>
+    <t>below surface</t>
+  </si>
+  <si>
+    <t>Flow Direction</t>
+  </si>
+  <si>
+    <t>Vertical downwards towards excavation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Total Flow Distance </t>
+  </si>
+  <si>
+    <t>L1 + L2 + L3</t>
+  </si>
+  <si>
+    <t>L total - L2 -L1</t>
+  </si>
+  <si>
+    <t>L3 (m)</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>Delta h</t>
+  </si>
+  <si>
+    <t>L total</t>
+  </si>
+  <si>
+    <t>head diff</t>
+  </si>
+  <si>
+    <t>Calculating Effective Hydraulic Conductivity</t>
+  </si>
+  <si>
+    <t>K eff</t>
+  </si>
+  <si>
+    <t>Ltotal</t>
+  </si>
+  <si>
+    <t>Sum(Li/Ki)</t>
+  </si>
+  <si>
+    <t>m/s</t>
+  </si>
+  <si>
+    <t>Average Hydraulic Gradient</t>
+  </si>
+  <si>
+    <t>Calculating speific discharge, hydraulic gradient, and head loss.</t>
+  </si>
+  <si>
+    <t>Specific Discharge</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>Keff * i</t>
+  </si>
+  <si>
+    <t>Computing Hydraulic Gradient</t>
+  </si>
+  <si>
+    <t>q * (Li/Ki)</t>
+  </si>
+  <si>
+    <t>Pw (roh water)</t>
+  </si>
+  <si>
+    <t>Delta h(i)</t>
+  </si>
+  <si>
+    <t>L (i)</t>
+  </si>
+  <si>
+    <t>i(i)</t>
+  </si>
+  <si>
+    <t>head diff(i)</t>
+  </si>
+  <si>
+    <t>head diff(Ss)</t>
+  </si>
+  <si>
+    <t>q * (L(Ss)/K(Ss))</t>
+  </si>
+  <si>
+    <t>Silt sand (Ss)</t>
+  </si>
+  <si>
+    <t>Silt sand (Lc)</t>
+  </si>
+  <si>
+    <t>head diff(Lc)</t>
+  </si>
+  <si>
+    <t>q * (L(Lc)/K(Lc))</t>
+  </si>
+  <si>
+    <t>Calculating total head loss</t>
+  </si>
+  <si>
+    <t>delta h Ss</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
+    <t>delta h Lc</t>
+  </si>
+  <si>
+    <t>Silt sand (Lgg)</t>
+  </si>
+  <si>
+    <t>head diff(Lgg)</t>
+  </si>
+  <si>
+    <t>q * (L(Lgg)/K(Lgg))</t>
+  </si>
+  <si>
+    <t>delta h Lgg</t>
+  </si>
+  <si>
+    <t>Total (m)</t>
   </si>
 </sst>
 </file>
@@ -336,9 +504,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -406,7 +574,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -461,8 +629,20 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -597,25 +777,65 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="10">
+  <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -632,158 +852,209 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="6" fillId="6" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="5" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="8" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="4" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="4" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="6" fillId="6" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="5" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="5" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="8" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="9" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="5" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="3" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="6" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="8" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="8" xfId="9" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" xfId="9" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="13" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="10" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="5" xfId="10" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="10" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="10">
-    <cellStyle name="20% - Accent3" xfId="8" builtinId="38"/>
-    <cellStyle name="20% - Accent6" xfId="9" builtinId="50"/>
+  <cellStyles count="11">
+    <cellStyle name="20% - Accent3" xfId="7" builtinId="38"/>
+    <cellStyle name="20% - Accent6" xfId="8" builtinId="50"/>
+    <cellStyle name="40% - Accent1" xfId="9" builtinId="31"/>
+    <cellStyle name="40% - Accent2" xfId="10" builtinId="35"/>
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
-    <cellStyle name="Calculation" xfId="6" builtinId="22"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Input" xfId="4" builtinId="20"/>
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="7" builtinId="10"/>
+    <cellStyle name="Note" xfId="6" builtinId="10"/>
     <cellStyle name="Output" xfId="5" builtinId="21"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -797,10 +1068,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1125,10 +1392,11 @@
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
     <col min="3" max="3" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.77734375" style="2" customWidth="1"/>
     <col min="5" max="5" width="7.44140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" style="2" customWidth="1"/>
-    <col min="7" max="8" width="8.88671875" style="2"/>
+    <col min="6" max="6" width="12.77734375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="2"/>
     <col min="9" max="9" width="9.5546875" style="2" customWidth="1"/>
     <col min="10" max="10" width="8.88671875" style="2"/>
     <col min="11" max="11" width="11.6640625" style="2" customWidth="1"/>
@@ -1141,64 +1409,64 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="H2" s="17" t="s">
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="H2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17" t="s">
+      <c r="I2" s="27"/>
+      <c r="J2" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="H3" s="17" t="s">
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="H3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17" t="s">
+      <c r="I3" s="27"/>
+      <c r="J3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="H4" s="17" t="s">
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="H4" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17" t="s">
+      <c r="I4" s="27"/>
+      <c r="J4" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="7" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1206,28 +1474,28 @@
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="7" t="s">
+      <c r="B11" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="33"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="8"/>
+      <c r="F11" s="36"/>
       <c r="G11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="6"/>
+      <c r="I11" s="31"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="8"/>
+      <c r="C12" s="36"/>
       <c r="D12" s="1" t="s">
         <v>11</v>
       </c>
@@ -1237,7 +1505,7 @@
       <c r="F12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="18">
         <f>((2*(0.05/5.16))+(0.05/9.87))*D13</f>
         <v>5.0475857142857148</v>
       </c>
@@ -1249,20 +1517,20 @@
       <c r="K12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L12" s="15" t="s">
+      <c r="L12" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="M12" s="16"/>
-      <c r="N12" s="12" t="s">
+      <c r="M12" s="40"/>
+      <c r="N12" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="32">
+      <c r="C13" s="34"/>
+      <c r="D13" s="18">
         <f>(22/7)*((5.16*5.16)/4)*(9.87)</f>
         <v>206.481528</v>
       </c>
@@ -1272,7 +1540,7 @@
       <c r="F13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="18">
         <f>SQRT(((2*(0.05/5.16))^2)+((0.05/9.87)^2))*D13</f>
         <v>4.1360331781452588</v>
       </c>
@@ -1284,17 +1552,17 @@
       <c r="K13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L13" s="30">
+      <c r="L13" s="16">
         <f>G13/D13</f>
         <v>2.003100818851582E-2</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="11"/>
+      <c r="B15" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="33"/>
+      <c r="D15" s="34"/>
       <c r="E15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1304,10 +1572,10 @@
       <c r="I15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="K15" s="8"/>
+      <c r="K15" s="36"/>
       <c r="L15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1319,14 +1587,14 @@
       <c r="B16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="22" t="s">
-        <v>94</v>
+      <c r="E16" s="11" t="s">
+        <v>91</v>
       </c>
       <c r="F16" s="1">
         <v>537.29999999999995</v>
@@ -1346,29 +1614,29 @@
       <c r="K16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="6">
         <f>(0.2)+(0.2)/1</f>
         <v>0.4</v>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="14">
         <f>L16/$I$17</f>
         <v>1.9493177387914238E-3</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P16" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="12" t="s">
+      <c r="P16" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="1"/>
@@ -1377,7 +1645,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1"/>
-      <c r="I17" s="12">
+      <c r="I17" s="6">
         <f>(F16-H16)/1</f>
         <v>205.19999999999993</v>
       </c>
@@ -1387,252 +1655,252 @@
       <c r="K17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="31">
+      <c r="L17" s="17">
         <f>(SQRT((0.2^2)+(0.2^2)))/1</f>
         <v>0.28284271247461906</v>
       </c>
-      <c r="M17" s="28">
+      <c r="M17" s="14">
         <f>L17/$I$17</f>
         <v>1.378375791786643E-3</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P17" s="29">
+      <c r="P17" s="15">
         <f>L17/I17</f>
         <v>1.378375791786643E-3</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B19" s="52" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
-      <c r="K19" s="52"/>
+      <c r="B19" s="55" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="55"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="52"/>
-      <c r="K20" s="52"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="55"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B21" s="52"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
-      <c r="K21" s="52"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="55"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="52"/>
-      <c r="K22" s="52"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="55"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="52"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="55"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="11"/>
+      <c r="E25" s="34"/>
       <c r="F25" s="1">
         <v>530.9</v>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="43">
         <f>F25/F26</f>
         <v>2.6705231388329986</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="J25" s="35">
+      <c r="J25" s="43">
         <f>SQRT((0.2/530.9)^2+((0.2+0.2)/(F26))^2)*G25</f>
         <v>5.4666544833054257E-3</v>
       </c>
-      <c r="L25" s="4" t="s">
+      <c r="L25" s="41" t="s">
         <v>33</v>
       </c>
       <c r="M25" s="1">
         <f>J25</f>
         <v>5.4666544833054257E-3</v>
       </c>
-      <c r="N25" s="35">
+      <c r="N25" s="43">
         <f>M25/M26</f>
         <v>2.0470350560955327E-3</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="9" t="s">
+      <c r="B26" s="42"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="11"/>
+      <c r="E26" s="34"/>
       <c r="F26" s="1">
         <f>F25-H16</f>
         <v>198.79999999999995</v>
       </c>
-      <c r="G26" s="36"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="36"/>
-      <c r="L26" s="5"/>
+      <c r="G26" s="44"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="44"/>
+      <c r="L26" s="42"/>
       <c r="M26" s="1">
         <f>G25</f>
         <v>2.6705231388329986</v>
       </c>
-      <c r="N26" s="36"/>
+      <c r="N26" s="44"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" s="11" t="s">
         <v>31</v>
       </c>
       <c r="E28" s="1">
         <f>F16-F25</f>
         <v>6.3999999999999773</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="28">
         <f>E28/E29</f>
         <v>1.2055000941796906E-2</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="I28" s="33">
+      <c r="I28" s="28">
         <f>SQRT((0.4/E28)^2+(0.2/F25)^2)*F28</f>
         <v>7.5345124521829037E-4</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="K28" s="41" t="s">
         <v>37</v>
       </c>
       <c r="L28" s="1">
         <f>I28</f>
         <v>7.5345124521829037E-4</v>
       </c>
-      <c r="M28" s="13">
+      <c r="M28" s="45">
         <f>L28/L29</f>
         <v>6.2501135325998713E-2</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="22" t="s">
+      <c r="B29" s="42"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="11" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="1">
         <f>F25</f>
         <v>530.9</v>
       </c>
-      <c r="F29" s="34"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="34"/>
-      <c r="K29" s="5"/>
+      <c r="F29" s="29"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="29"/>
+      <c r="K29" s="42"/>
       <c r="L29" s="1">
         <f>F28</f>
         <v>1.2055000941796906E-2</v>
       </c>
-      <c r="M29" s="14"/>
+      <c r="M29" s="46"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="11" t="s">
         <v>32</v>
       </c>
       <c r="E31" s="1">
         <f>F25</f>
         <v>530.9</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="43">
         <f>E31/E32</f>
         <v>2.5872319688109169</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="I31" s="35">
+      <c r="I31" s="43">
         <f>SQRT((0.2/E29)^2+(P17)^2)*F31</f>
         <v>3.6969696810700515E-3</v>
       </c>
-      <c r="K31" s="4" t="s">
+      <c r="K31" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="43">
         <f>I31/F31</f>
         <v>1.4289285713987086E-3</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="22" t="s">
+      <c r="B32" s="42"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E32" s="1">
         <f>I17</f>
         <v>205.19999999999993</v>
       </c>
-      <c r="F32" s="36"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="36"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="36"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F32" s="44"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="44"/>
+      <c r="K32" s="42"/>
+      <c r="L32" s="44"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
@@ -1642,7 +1910,7 @@
       <c r="C34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -1657,25 +1925,25 @@
       <c r="I34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J34" s="22" t="s">
+      <c r="J34" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="11" t="s">
         <v>30</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
-      <c r="J35" s="22" t="s">
+      <c r="J35" s="11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
         <v>44</v>
       </c>
@@ -1703,7 +1971,7 @@
         <v>3.2193158953722323E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -1719,14 +1987,14 @@
         <v>1.0321931589537223</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="6">
         <f>(D36/D37)-1</f>
         <v>3.2193158953722323E-2</v>
       </c>
@@ -1738,49 +2006,53 @@
       <c r="I38" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J38" s="12">
+      <c r="J38" s="6">
         <f>J36/J37</f>
         <v>3.1189083820662756E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="20" t="s">
+      <c r="B42" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="F42" s="21" t="s">
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="F42" s="10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D43" s="22" t="s">
+      <c r="D43" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
-      <c r="D44" s="22" t="s">
+      <c r="D44" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="39" t="s">
+      <c r="F44" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="G44" s="39"/>
-      <c r="H44" s="39"/>
-      <c r="I44" s="39"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="26"/>
+      <c r="K44" s="26"/>
+      <c r="L44" s="26"/>
+      <c r="M44" s="26"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>47</v>
       </c>
@@ -1791,42 +2063,84 @@
         <f>(F28*G25)</f>
         <v>3.2193158953722226E-2</v>
       </c>
-      <c r="F45" s="39"/>
-      <c r="G45" s="39"/>
-      <c r="H45" s="39"/>
-      <c r="I45" s="39"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="26"/>
+      <c r="M45" s="26"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1">
         <f>D38</f>
         <v>3.2193158953722323E-2</v>
       </c>
-      <c r="F46" s="39"/>
-      <c r="G46" s="39"/>
-      <c r="H46" s="39"/>
-      <c r="I46" s="39"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="26"/>
+      <c r="K46" s="26"/>
+      <c r="L46" s="26"/>
+      <c r="M46" s="26"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D47" s="12">
+      <c r="D47" s="6">
         <f>D45/D46</f>
         <v>0.999999999999997</v>
       </c>
-      <c r="F47" s="39"/>
-      <c r="G47" s="39"/>
-      <c r="H47" s="39"/>
-      <c r="I47" s="39"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="26"/>
+      <c r="K47" s="26"/>
+      <c r="L47" s="26"/>
+      <c r="M47" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="F44:I47"/>
+    <mergeCell ref="F44:M47"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="M28:M29"/>
+    <mergeCell ref="K28:K29"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B19:K23"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="J3:L3"/>
@@ -1842,36 +2156,6 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="M28:M29"/>
-    <mergeCell ref="K28:K29"/>
-    <mergeCell ref="K31:K32"/>
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="B31:B32"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1880,7 +2164,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC3F6AF4-9254-4448-BB25-202C93612D60}">
-  <dimension ref="A2:K44"/>
+  <dimension ref="A2:I44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="2" customWidth="1"/>
@@ -1894,400 +2178,413 @@
     <col min="9" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="24" t="s">
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="68"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="24"/>
-      <c r="C4" s="24" t="s">
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="12">
         <v>1.2250000000000001</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="13">
         <v>1.8099999999999999E-5</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="24"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="24" t="s">
+      <c r="I4" s="12"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="24"/>
-      <c r="C6" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="24">
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="12"/>
+      <c r="C6" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" s="12">
         <v>999.1</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="13">
         <v>8.8999999999999995E-4</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="I6" s="24"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="24"/>
-      <c r="C8" s="25" t="s">
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="12"/>
+      <c r="C8" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="24"/>
-      <c r="C9" s="25" t="s">
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="12"/>
+      <c r="C9" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="24">
+      <c r="D9" s="49"/>
+      <c r="E9" s="12">
         <v>6</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="24" t="s">
+      <c r="G9" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="12">
         <v>9.81</v>
       </c>
-      <c r="I9" s="24" t="s">
+      <c r="I9" s="12" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="24"/>
-      <c r="C10" s="25" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="12"/>
+      <c r="C10" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="24">
+      <c r="D10" s="49"/>
+      <c r="E10" s="12">
         <v>15</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="47" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+    </row>
+    <row r="13" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="1"/>
-      <c r="C18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1000</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
+      <c r="B18" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B19" s="1"/>
-      <c r="C19" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="H19" s="41" t="s">
-        <v>87</v>
-      </c>
+      <c r="C19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1000</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
-      <c r="C20" s="42">
-        <v>25</v>
-      </c>
-      <c r="D20" s="42">
-        <f>C20*$D$18</f>
-        <v>25000</v>
-      </c>
-      <c r="E20" s="43">
-        <v>47.8</v>
-      </c>
-      <c r="F20" s="42">
-        <f>D20/($D$4*$H$9)</f>
-        <v>2080.3428405001141</v>
-      </c>
-      <c r="G20" s="43">
-        <f>E20/F20</f>
-        <v>2.2976982000000003E-2</v>
-      </c>
-      <c r="H20" s="44">
-        <f>(G24*G4)/(D4*H9)</f>
-        <v>3.3786666666666674E-8</v>
+      <c r="C20" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>86</v>
       </c>
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
-      <c r="C21" s="42">
-        <v>50</v>
-      </c>
-      <c r="D21" s="42">
-        <f>C21*$D$18</f>
-        <v>50000</v>
-      </c>
-      <c r="E21" s="43">
-        <v>94.9</v>
-      </c>
-      <c r="F21" s="42">
-        <f t="shared" ref="F21:F23" si="0">D21/($D$4*$H$9)</f>
-        <v>4160.6856810002282</v>
-      </c>
-      <c r="G21" s="43">
-        <f t="shared" ref="G21:G23" si="1">E21/F21</f>
-        <v>2.2808740500000004E-2</v>
-      </c>
-      <c r="H21" s="44"/>
+      <c r="C21" s="9">
+        <v>25</v>
+      </c>
+      <c r="D21" s="9">
+        <f>C21*$D$19</f>
+        <v>25000</v>
+      </c>
+      <c r="E21" s="21">
+        <v>47.8</v>
+      </c>
+      <c r="F21" s="9">
+        <f>D21/($D$4*$H$9)</f>
+        <v>2080.3428405001141</v>
+      </c>
+      <c r="G21" s="21">
+        <f>E21/F21</f>
+        <v>2.2976982000000003E-2</v>
+      </c>
+      <c r="H21" s="56">
+        <f>(G25*G4)/(D4*H9)</f>
+        <v>3.3786666666666674E-8</v>
+      </c>
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B22" s="1"/>
-      <c r="C22" s="42">
+      <c r="C22" s="9">
+        <v>50</v>
+      </c>
+      <c r="D22" s="9">
+        <f>C22*$D$19</f>
+        <v>50000</v>
+      </c>
+      <c r="E22" s="21">
+        <v>94.9</v>
+      </c>
+      <c r="F22" s="9">
+        <f t="shared" ref="F22:F24" si="0">D22/($D$4*$H$9)</f>
+        <v>4160.6856810002282</v>
+      </c>
+      <c r="G22" s="21">
+        <f t="shared" ref="G22:G24" si="1">E22/F22</f>
+        <v>2.2808740500000004E-2</v>
+      </c>
+      <c r="H22" s="57"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B23" s="1"/>
+      <c r="C23" s="9">
         <v>75</v>
       </c>
-      <c r="D22" s="42">
-        <f>C22*$D$18</f>
+      <c r="D23" s="9">
+        <f>C23*$D$19</f>
         <v>75000</v>
       </c>
-      <c r="E22" s="43">
+      <c r="E23" s="21">
         <v>134</v>
       </c>
-      <c r="F22" s="42">
+      <c r="F23" s="9">
         <f t="shared" si="0"/>
         <v>6241.0285215003432</v>
       </c>
-      <c r="G22" s="43">
+      <c r="G23" s="21">
         <f t="shared" si="1"/>
         <v>2.1470820000000002E-2</v>
       </c>
-      <c r="H22" s="44"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="1"/>
-      <c r="C23" s="42">
+      <c r="H23" s="57"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B24" s="1"/>
+      <c r="C24" s="9">
         <v>100</v>
       </c>
-      <c r="D23" s="42">
-        <f>C23*$D$18</f>
+      <c r="D24" s="9">
+        <f>C24*$D$19</f>
         <v>100000</v>
       </c>
-      <c r="E23" s="43">
+      <c r="E24" s="21">
         <v>187</v>
       </c>
-      <c r="F23" s="42">
+      <c r="F24" s="9">
         <f t="shared" si="0"/>
         <v>8321.3713620004564</v>
       </c>
-      <c r="G23" s="43">
+      <c r="G24" s="21">
         <f t="shared" si="1"/>
         <v>2.2472257500000002E-2</v>
       </c>
-      <c r="H23" s="44"/>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B24" s="19" t="s">
+      <c r="H24" s="57"/>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B25" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="45">
-        <f>AVERAGE(G20:G23)</f>
-        <v>2.2432200000000006E-2</v>
-      </c>
-      <c r="H24" s="44"/>
-      <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
+      <c r="G25" s="23">
+        <f>AVERAGE(G21:G24)</f>
+        <v>2.2432200000000006E-2</v>
+      </c>
+      <c r="H25" s="58"/>
       <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1">
+        <v>2.24E-4</v>
+      </c>
+      <c r="H26" s="70">
+        <f>(G26*G4)/(D4*H9)</f>
+        <v>3.3738168050094649E-10</v>
+      </c>
+      <c r="I26" s="1"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
+      <c r="B28" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="47"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
-      <c r="C29" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" s="40">
+      <c r="C29" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="61">
         <v>70</v>
       </c>
-      <c r="E29" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="F29" s="40">
+      <c r="E29" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F29" s="61">
         <v>7200</v>
       </c>
       <c r="G29" s="1"/>
@@ -2296,53 +2593,53 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B30" s="1"/>
-      <c r="C30" s="40" t="s">
+      <c r="C30" s="59" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" s="62">
+        <v>11</v>
+      </c>
+      <c r="E30" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="D30" s="40">
-        <v>11</v>
-      </c>
-      <c r="E30" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="F30" s="40">
+      <c r="F30" s="62">
         <v>871</v>
       </c>
-      <c r="G30" s="1"/>
+      <c r="G30" s="4"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B31" s="1"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B32" s="1"/>
-      <c r="C32" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="D32" s="50">
+      <c r="C32" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="65">
         <f>D29/D30</f>
         <v>6.3636363636363633</v>
       </c>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B33" s="1"/>
-      <c r="C33" s="40" t="s">
+      <c r="C33" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="D33" s="50">
+      <c r="D33" s="65">
         <f>LN(D32)</f>
         <v>1.8505999692509885</v>
       </c>
@@ -2354,10 +2651,10 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B34" s="1"/>
-      <c r="C34" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="48">
+      <c r="C34" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="D34" s="25">
         <f>((F30)/ ((22/7)*(6/2)^2*(F29)))*(LN(70/11))</f>
         <v>7.9146380559226136E-3</v>
       </c>
@@ -2369,17 +2666,17 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B35" s="1"/>
-      <c r="C35" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="D35" s="21">
+      <c r="C35" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="10">
         <f>D34*(0.00089)/(999.1*9.81)</f>
         <v>7.1869247764079674E-10</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F35" s="45">
+        <v>89</v>
+      </c>
+      <c r="F35" s="23">
         <v>7.19E-10</v>
       </c>
       <c r="G35" s="1"/>
@@ -2400,90 +2697,94 @@
       <c r="A38" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="47"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="47"/>
-      <c r="H38" s="47"/>
-      <c r="I38" s="47"/>
+      <c r="B38" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="48"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="48"/>
+      <c r="I38" s="48"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="47"/>
-      <c r="C39" s="47"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="47"/>
-      <c r="I39" s="47"/>
+      <c r="B39" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" s="48"/>
+      <c r="D39" s="48"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="48"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="47"/>
-      <c r="C40" s="47"/>
-      <c r="D40" s="47"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="47"/>
-      <c r="I40" s="47"/>
+      <c r="B40" s="48"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B41" s="47"/>
-      <c r="C41" s="47"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="47"/>
-      <c r="G41" s="47"/>
-      <c r="H41" s="47"/>
-      <c r="I41" s="47"/>
+      <c r="B41" s="48"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="48"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B42" s="47"/>
-      <c r="C42" s="47"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="47"/>
-      <c r="I42" s="47"/>
+      <c r="B42" s="48"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="48"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="48"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B43" s="47"/>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="47"/>
-      <c r="I43" s="47"/>
+      <c r="B43" s="48"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="48"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B44" s="47"/>
-      <c r="C44" s="47"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="47"/>
-      <c r="I44" s="47"/>
+      <c r="B44" s="48"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="48"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="B13:I16"/>
+    <mergeCell ref="B2:I2"/>
     <mergeCell ref="B28:I28"/>
-    <mergeCell ref="B13:I15"/>
     <mergeCell ref="B39:I44"/>
     <mergeCell ref="B38:I38"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="H20:H24"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="H21:H25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2491,9 +2792,724 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D282ACF5-C05D-4510-AA94-B01BF0206C06}">
-  <dimension ref="A1"/>
+  <dimension ref="A2:G62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="30"/>
+      <c r="D3" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="E3" s="70">
+        <v>5.8E-5</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="30"/>
+      <c r="D4" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="E4" s="70">
+        <v>3.5999999999999998E-8</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="30"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="70">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="30"/>
+      <c r="D6" s="1">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="30"/>
+      <c r="D7" s="1">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="30"/>
+      <c r="D8" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="30"/>
+      <c r="D9" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" s="6">
+        <f>D6-D3-D4</f>
+        <v>8</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="1">
+        <f>D8</f>
+        <v>1.5</v>
+      </c>
+      <c r="F18" s="6">
+        <f>E18/E19</f>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="1">
+        <f>D6</f>
+        <v>14</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="1">
+        <f>E19</f>
+        <v>14</v>
+      </c>
+      <c r="E25" s="23">
+        <f>D25/D26</f>
+        <v>1.2490984311009928E-6</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="70">
+        <f>((D3/E3)+(D4/E4)+(E14/E5))</f>
+        <v>11208083.887880621</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="E30" s="22">
+        <f>(E25*F18)</f>
+        <v>1.3383197476082065E-7</v>
+      </c>
+      <c r="F30" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="G30" s="24"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="G36" s="24"/>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="C38" s="48"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="G39" s="48"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" s="52">
+        <f>(E30*D3)/E3</f>
+        <v>1.2921707907941303E-2</v>
+      </c>
+      <c r="G40" s="52"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B42" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="C42" s="48"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="E43" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="G43" s="48"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B44" s="24"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" s="52">
+        <f>(E30*D4)/E4</f>
+        <v>1.4870219417868964</v>
+      </c>
+      <c r="G44" s="52"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B46" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" s="48"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B47" s="24"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F47" s="48" t="s">
+        <v>150</v>
+      </c>
+      <c r="G47" s="48"/>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B48" s="24"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="E48" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F48" s="52">
+        <f>(E30*E14)/E5</f>
+        <v>5.6350305162450804E-5</v>
+      </c>
+      <c r="G48" s="52"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B49" s="24"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B50" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="C50" s="48"/>
+      <c r="D50" s="48"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B51" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="D51" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E51" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B52" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" s="22">
+        <f>F40+F44+F48</f>
+        <v>1.5000000000000002</v>
+      </c>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B54" s="48"/>
+      <c r="C54" s="48"/>
+      <c r="D54" s="48"/>
+      <c r="E54" s="48"/>
+      <c r="F54" s="48"/>
+      <c r="G54" s="48"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B55" s="48"/>
+      <c r="C55" s="48"/>
+      <c r="D55" s="48"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B56" s="48"/>
+      <c r="C56" s="48"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="48"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B57" s="48"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="48"/>
+      <c r="E57" s="48"/>
+      <c r="F57" s="48"/>
+      <c r="G57" s="48"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B58" s="48"/>
+      <c r="C58" s="48"/>
+      <c r="D58" s="48"/>
+      <c r="E58" s="48"/>
+      <c r="F58" s="48"/>
+      <c r="G58" s="48"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B59" s="48"/>
+      <c r="C59" s="48"/>
+      <c r="D59" s="48"/>
+      <c r="E59" s="48"/>
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B60" s="48"/>
+      <c r="C60" s="48"/>
+      <c r="D60" s="48"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B54:G60"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Excel.temp/GOPH 457 MIDTERM 1.xlsx
+++ b/Excel.temp/GOPH 457 MIDTERM 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bddd1913fb6f10a7/Documents/SCHOOL/GOPH 457 L01 - (Winter 2025) - Physical Properties of Minerals^J Soils and Rock - 2132025 - 835 AM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1170" documentId="8_{A6E124A9-3F37-4D6B-94E3-22EA175D76B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68DE15F4-68DF-4525-9993-4E7F14968AF1}"/>
+  <xr:revisionPtr revIDLastSave="1223" documentId="8_{A6E124A9-3F37-4D6B-94E3-22EA175D76B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35C5B5A7-FEBD-4739-B270-02A9C0808F0E}"/>
   <bookViews>
-    <workbookView xWindow="36765" yWindow="0" windowWidth="12660" windowHeight="16305" activeTab="2" xr2:uid="{324697F0-F716-4973-9DEE-7915F077F450}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{324697F0-F716-4973-9DEE-7915F077F450}"/>
   </bookViews>
   <sheets>
     <sheet name="Q1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="164">
   <si>
     <t>r = 2.58 ± 0.05 cm</t>
   </si>
@@ -400,9 +400,6 @@
     <t>L total</t>
   </si>
   <si>
-    <t>head diff</t>
-  </si>
-  <si>
     <t>Calculating Effective Hydraulic Conductivity</t>
   </si>
   <si>
@@ -497,6 +494,42 @@
   </si>
   <si>
     <t>Total (m)</t>
+  </si>
+  <si>
+    <t>Specific Discharge Calculations</t>
+  </si>
+  <si>
+    <t>head difference</t>
+  </si>
+  <si>
+    <t>q * Area</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>Dimensions (m)</t>
+  </si>
+  <si>
+    <t>Width *Length</t>
+  </si>
+  <si>
+    <t>Area (m2)</t>
+  </si>
+  <si>
+    <t>Flow rate (Q) (m3/s)</t>
+  </si>
+  <si>
+    <t>Convert to L/hr</t>
+  </si>
+  <si>
+    <t>Q * 3600</t>
+  </si>
+  <si>
+    <t>Flow rate (Q) (L/hr)</t>
   </si>
 </sst>
 </file>
@@ -508,7 +541,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,8 +606,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -639,6 +679,11 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
       </patternFill>
     </fill>
   </fills>
@@ -822,7 +867,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="11">
+  <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -834,8 +879,9 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -912,143 +958,153 @@
     <xf numFmtId="11" fontId="5" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="8" xfId="9" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" xfId="9" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="13" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="4" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="10" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="5" xfId="10" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="10" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="7" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="3" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="8" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="11" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="3" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="8" xfId="9" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" xfId="9" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="13" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="10" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="5" xfId="10" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="10" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="11">
+  <cellStyles count="12">
     <cellStyle name="20% - Accent3" xfId="7" builtinId="38"/>
     <cellStyle name="20% - Accent6" xfId="8" builtinId="50"/>
     <cellStyle name="40% - Accent1" xfId="9" builtinId="31"/>
     <cellStyle name="40% - Accent2" xfId="10" builtinId="35"/>
+    <cellStyle name="Accent6" xfId="11" builtinId="49"/>
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Input" xfId="4" builtinId="20"/>
@@ -1068,6 +1124,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1409,58 +1469,58 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="H2" s="27" t="s">
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="H2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27" t="s">
+      <c r="I2" s="55"/>
+      <c r="J2" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="H3" s="27" t="s">
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="H3" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27" t="s">
+      <c r="I3" s="55"/>
+      <c r="J3" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="H4" s="27" t="s">
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="H4" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27" t="s">
+      <c r="I4" s="55"/>
+      <c r="J4" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
@@ -1474,28 +1534,28 @@
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="35" t="s">
+      <c r="C11" s="53"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="36"/>
+      <c r="F11" s="46"/>
       <c r="G11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="31" t="s">
+      <c r="H11" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="31"/>
+      <c r="I11" s="57"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="36"/>
+      <c r="C12" s="46"/>
       <c r="D12" s="1" t="s">
         <v>11</v>
       </c>
@@ -1509,27 +1569,27 @@
         <f>((2*(0.05/5.16))+(0.05/9.87))*D13</f>
         <v>5.0475857142857148</v>
       </c>
-      <c r="H12" s="37">
+      <c r="H12" s="51">
         <f>G12/$D$13</f>
         <v>2.4445701090926229E-2</v>
       </c>
-      <c r="I12" s="38"/>
+      <c r="I12" s="52"/>
       <c r="K12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L12" s="39" t="s">
+      <c r="L12" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="M12" s="40"/>
+      <c r="M12" s="48"/>
       <c r="N12" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="18">
         <f>(22/7)*((5.16*5.16)/4)*(9.87)</f>
         <v>206.481528</v>
@@ -1544,11 +1604,11 @@
         <f>SQRT(((2*(0.05/5.16))^2)+((0.05/9.87)^2))*D13</f>
         <v>4.1360331781452588</v>
       </c>
-      <c r="H13" s="37">
+      <c r="H13" s="51">
         <f>G13/$D$13</f>
         <v>2.003100818851582E-2</v>
       </c>
-      <c r="I13" s="38"/>
+      <c r="I13" s="52"/>
       <c r="K13" s="1" t="s">
         <v>25</v>
       </c>
@@ -1558,11 +1618,11 @@
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="34"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="50"/>
       <c r="E15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1572,10 +1632,10 @@
       <c r="I15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="35" t="s">
+      <c r="J15" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="K15" s="36"/>
+      <c r="K15" s="46"/>
       <c r="L15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1625,10 +1685,10 @@
       <c r="O16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P16" s="39" t="s">
+      <c r="P16" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="Q16" s="40"/>
+      <c r="Q16" s="48"/>
       <c r="R16" s="6" t="s">
         <v>11</v>
       </c>
@@ -1672,133 +1732,133 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="55"/>
-      <c r="K19" s="55"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="54"/>
+      <c r="K19" s="54"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B20" s="55"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="55"/>
-      <c r="K20" s="55"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
+      <c r="K20" s="54"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B21" s="55"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="55"/>
-      <c r="K21" s="55"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
+      <c r="K21" s="54"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B22" s="55"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="55"/>
-      <c r="K22" s="55"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="55"/>
-      <c r="I23" s="55"/>
-      <c r="J23" s="55"/>
-      <c r="K23" s="55"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="C25" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="34"/>
+      <c r="E25" s="50"/>
       <c r="F25" s="1">
         <v>530.9</v>
       </c>
-      <c r="G25" s="43">
+      <c r="G25" s="41">
         <f>F25/F26</f>
         <v>2.6705231388329986</v>
       </c>
-      <c r="I25" s="41" t="s">
+      <c r="I25" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="J25" s="43">
+      <c r="J25" s="41">
         <f>SQRT((0.2/530.9)^2+((0.2+0.2)/(F26))^2)*G25</f>
         <v>5.4666544833054257E-3</v>
       </c>
-      <c r="L25" s="41" t="s">
+      <c r="L25" s="37" t="s">
         <v>33</v>
       </c>
       <c r="M25" s="1">
         <f>J25</f>
         <v>5.4666544833054257E-3</v>
       </c>
-      <c r="N25" s="43">
+      <c r="N25" s="41">
         <f>M25/M26</f>
         <v>2.0470350560955327E-3</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B26" s="42"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="32" t="s">
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="34"/>
+      <c r="E26" s="50"/>
       <c r="F26" s="1">
         <f>F25-H16</f>
         <v>198.79999999999995</v>
       </c>
-      <c r="G26" s="44"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="44"/>
-      <c r="L26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="42"/>
+      <c r="L26" s="38"/>
       <c r="M26" s="1">
         <f>G25</f>
         <v>2.6705231388329986</v>
       </c>
-      <c r="N26" s="44"/>
+      <c r="N26" s="42"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="41" t="s">
+      <c r="C28" s="37" t="s">
         <v>24</v>
       </c>
       <c r="D28" s="11" t="s">
@@ -1808,32 +1868,32 @@
         <f>F16-F25</f>
         <v>6.3999999999999773</v>
       </c>
-      <c r="F28" s="28">
+      <c r="F28" s="39">
         <f>E28/E29</f>
         <v>1.2055000941796906E-2</v>
       </c>
-      <c r="H28" s="41" t="s">
+      <c r="H28" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="I28" s="28">
+      <c r="I28" s="39">
         <f>SQRT((0.4/E28)^2+(0.2/F25)^2)*F28</f>
         <v>7.5345124521829037E-4</v>
       </c>
-      <c r="K28" s="41" t="s">
+      <c r="K28" s="37" t="s">
         <v>37</v>
       </c>
       <c r="L28" s="1">
         <f>I28</f>
         <v>7.5345124521829037E-4</v>
       </c>
-      <c r="M28" s="45">
+      <c r="M28" s="43">
         <f>L28/L29</f>
         <v>6.2501135325998713E-2</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B29" s="42"/>
-      <c r="C29" s="42"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
       <c r="D29" s="11" t="s">
         <v>32</v>
       </c>
@@ -1841,21 +1901,21 @@
         <f>F25</f>
         <v>530.9</v>
       </c>
-      <c r="F29" s="29"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="29"/>
-      <c r="K29" s="42"/>
+      <c r="F29" s="40"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="40"/>
+      <c r="K29" s="38"/>
       <c r="L29" s="1">
         <f>F28</f>
         <v>1.2055000941796906E-2</v>
       </c>
-      <c r="M29" s="46"/>
+      <c r="M29" s="44"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C31" s="37" t="s">
         <v>24</v>
       </c>
       <c r="D31" s="11" t="s">
@@ -1865,28 +1925,28 @@
         <f>F25</f>
         <v>530.9</v>
       </c>
-      <c r="F31" s="43">
+      <c r="F31" s="41">
         <f>E31/E32</f>
         <v>2.5872319688109169</v>
       </c>
-      <c r="H31" s="41" t="s">
+      <c r="H31" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="I31" s="43">
+      <c r="I31" s="41">
         <f>SQRT((0.2/E29)^2+(P17)^2)*F31</f>
         <v>3.6969696810700515E-3</v>
       </c>
-      <c r="K31" s="41" t="s">
+      <c r="K31" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="L31" s="43">
+      <c r="L31" s="41">
         <f>I31/F31</f>
         <v>1.4289285713987086E-3</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B32" s="42"/>
-      <c r="C32" s="42"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
       <c r="D32" s="11" t="s">
         <v>9</v>
       </c>
@@ -1894,11 +1954,11 @@
         <f>I17</f>
         <v>205.19999999999993</v>
       </c>
-      <c r="F32" s="44"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="44"/>
-      <c r="K32" s="42"/>
-      <c r="L32" s="44"/>
+      <c r="F32" s="42"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="42"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="42"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
@@ -2015,11 +2075,11 @@
       <c r="A42" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="30" t="s">
+      <c r="B42" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56"/>
       <c r="F42" s="10" t="s">
         <v>49</v>
       </c>
@@ -2041,16 +2101,16 @@
       <c r="D44" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="26" t="s">
+      <c r="F44" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="G44" s="26"/>
-      <c r="H44" s="26"/>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
-      <c r="K44" s="26"/>
-      <c r="L44" s="26"/>
-      <c r="M44" s="26"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="36"/>
+      <c r="M44" s="36"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
@@ -2063,14 +2123,14 @@
         <f>(F28*G25)</f>
         <v>3.2193158953722226E-2</v>
       </c>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
-      <c r="K45" s="26"/>
-      <c r="L45" s="26"/>
-      <c r="M45" s="26"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="36"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="36"/>
+      <c r="J45" s="36"/>
+      <c r="K45" s="36"/>
+      <c r="L45" s="36"/>
+      <c r="M45" s="36"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B46" s="1"/>
@@ -2079,14 +2139,14 @@
         <f>D38</f>
         <v>3.2193158953722323E-2</v>
       </c>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="26"/>
-      <c r="K46" s="26"/>
-      <c r="L46" s="26"/>
-      <c r="M46" s="26"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="36"/>
+      <c r="M46" s="36"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
@@ -2099,17 +2159,47 @@
         <f>D45/D46</f>
         <v>0.999999999999997</v>
       </c>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="26"/>
-      <c r="K47" s="26"/>
-      <c r="L47" s="26"/>
-      <c r="M47" s="26"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="36"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="36"/>
+      <c r="J47" s="36"/>
+      <c r="K47" s="36"/>
+      <c r="L47" s="36"/>
+      <c r="M47" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B19:K23"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J25:J26"/>
     <mergeCell ref="F44:M47"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="C28:C29"/>
@@ -2124,38 +2214,8 @@
     <mergeCell ref="L31:L32"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="H28:H29"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B19:K23"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="J4:L4"/>
     <mergeCell ref="I28:I29"/>
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E11:F11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2182,30 +2242,30 @@
       <c r="A2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="68"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="65"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="12"/>
@@ -2233,20 +2293,20 @@
       <c r="B5" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="49" t="s">
+      <c r="C5" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="12"/>
       <c r="C6" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D6" s="12">
         <v>999.1</v>
@@ -2277,11 +2337,11 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="12"/>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
@@ -2289,10 +2349,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="12"/>
-      <c r="C9" s="49" t="s">
+      <c r="C9" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="49"/>
+      <c r="D9" s="60"/>
       <c r="E9" s="12">
         <v>6</v>
       </c>
@@ -2311,10 +2371,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="12"/>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="49"/>
+      <c r="D10" s="60"/>
       <c r="E10" s="12">
         <v>15</v>
       </c>
@@ -2329,73 +2389,73 @@
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="48"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="62"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="59"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B19" s="1"/>
@@ -2453,7 +2513,7 @@
         <f>E21/F21</f>
         <v>2.2976982000000003E-2</v>
       </c>
-      <c r="H21" s="56">
+      <c r="H21" s="67">
         <f>(G25*G4)/(D4*H9)</f>
         <v>3.3786666666666674E-8</v>
       </c>
@@ -2479,7 +2539,7 @@
         <f t="shared" ref="G22:G24" si="1">E22/F22</f>
         <v>2.2808740500000004E-2</v>
       </c>
-      <c r="H22" s="57"/>
+      <c r="H22" s="68"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -2502,7 +2562,7 @@
         <f t="shared" si="1"/>
         <v>2.1470820000000002E-2</v>
       </c>
-      <c r="H23" s="57"/>
+      <c r="H23" s="68"/>
       <c r="I23" s="1"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -2525,7 +2585,7 @@
         <f t="shared" si="1"/>
         <v>2.2472257500000002E-2</v>
       </c>
-      <c r="H24" s="57"/>
+      <c r="H24" s="68"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -2540,7 +2600,7 @@
         <f>AVERAGE(G21:G24)</f>
         <v>2.2432200000000006E-2</v>
       </c>
-      <c r="H25" s="58"/>
+      <c r="H25" s="69"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
@@ -2552,7 +2612,7 @@
       <c r="G26" s="1">
         <v>2.24E-4</v>
       </c>
-      <c r="H26" s="70">
+      <c r="H26" s="35">
         <f>(G26*G4)/(D4*H9)</f>
         <v>3.3738168050094649E-10</v>
       </c>
@@ -2562,29 +2622,29 @@
       <c r="A28" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="66"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
       <c r="C29" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="D29" s="61">
+      <c r="D29" s="29">
         <v>70</v>
       </c>
       <c r="E29" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="F29" s="61">
+      <c r="F29" s="29">
         <v>7200</v>
       </c>
       <c r="G29" s="1"/>
@@ -2593,16 +2653,16 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B30" s="1"/>
-      <c r="C30" s="59" t="s">
+      <c r="C30" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="D30" s="62">
+      <c r="D30" s="30">
         <v>11</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="F30" s="62">
+      <c r="F30" s="30">
         <v>871</v>
       </c>
       <c r="G30" s="4"/>
@@ -2611,20 +2671,20 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B31" s="1"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="60"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B32" s="1"/>
-      <c r="C32" s="63" t="s">
+      <c r="C32" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="65">
+      <c r="D32" s="33">
         <f>D29/D30</f>
         <v>6.3636363636363633</v>
       </c>
@@ -2636,10 +2696,10 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B33" s="1"/>
-      <c r="C33" s="64" t="s">
+      <c r="C33" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="D33" s="65">
+      <c r="D33" s="33">
         <f>LN(D32)</f>
         <v>1.8505999692509885</v>
       </c>
@@ -2697,87 +2757,81 @@
       <c r="A38" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="48" t="s">
+      <c r="B38" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="48"/>
+      <c r="C38" s="62"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
+      <c r="G38" s="62"/>
+      <c r="H38" s="62"/>
+      <c r="I38" s="62"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="48" t="s">
+      <c r="B39" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="C39" s="48"/>
-      <c r="D39" s="48"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48"/>
+      <c r="C39" s="62"/>
+      <c r="D39" s="62"/>
+      <c r="E39" s="62"/>
+      <c r="F39" s="62"/>
+      <c r="G39" s="62"/>
+      <c r="H39" s="62"/>
+      <c r="I39" s="62"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="48"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48"/>
+      <c r="B40" s="62"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="62"/>
+      <c r="I40" s="62"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B41" s="48"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48"/>
+      <c r="B41" s="62"/>
+      <c r="C41" s="62"/>
+      <c r="D41" s="62"/>
+      <c r="E41" s="62"/>
+      <c r="F41" s="62"/>
+      <c r="G41" s="62"/>
+      <c r="H41" s="62"/>
+      <c r="I41" s="62"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B42" s="48"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="48"/>
+      <c r="B42" s="62"/>
+      <c r="C42" s="62"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="62"/>
+      <c r="I42" s="62"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B43" s="48"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48"/>
+      <c r="B43" s="62"/>
+      <c r="C43" s="62"/>
+      <c r="D43" s="62"/>
+      <c r="E43" s="62"/>
+      <c r="F43" s="62"/>
+      <c r="G43" s="62"/>
+      <c r="H43" s="62"/>
+      <c r="I43" s="62"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B44" s="48"/>
-      <c r="C44" s="48"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="48"/>
+      <c r="B44" s="62"/>
+      <c r="C44" s="62"/>
+      <c r="D44" s="62"/>
+      <c r="E44" s="62"/>
+      <c r="F44" s="62"/>
+      <c r="G44" s="62"/>
+      <c r="H44" s="62"/>
+      <c r="I44" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B18:I18"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="B13:I16"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B28:I28"/>
     <mergeCell ref="B39:I44"/>
@@ -2785,6 +2839,12 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="H21:H25"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="B13:I16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2792,22 +2852,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D282ACF5-C05D-4510-AA94-B01BF0206C06}">
-  <dimension ref="A2:G62"/>
+  <dimension ref="A2:G70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="9.77734375" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" customWidth="1"/>
     <col min="4" max="4" width="11.88671875" customWidth="1"/>
     <col min="5" max="5" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="55"/>
+      <c r="C2" s="54"/>
       <c r="D2" s="1" t="s">
         <v>102</v>
       </c>
@@ -2818,50 +2879,50 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="30"/>
+      <c r="C3" s="56"/>
       <c r="D3" s="1">
         <v>5.6</v>
       </c>
-      <c r="E3" s="70">
+      <c r="E3" s="35">
         <v>5.8E-5</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="30"/>
+      <c r="C4" s="56"/>
       <c r="D4" s="1">
         <v>0.4</v>
       </c>
-      <c r="E4" s="70">
+      <c r="E4" s="35">
         <v>3.5999999999999998E-8</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="30"/>
+      <c r="C5" s="56"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="70">
+      <c r="E5" s="35">
         <v>1.9E-2</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="30"/>
+      <c r="C6" s="56"/>
       <c r="D6" s="1">
         <v>14</v>
       </c>
@@ -2870,10 +2931,10 @@
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="30"/>
+      <c r="C7" s="56"/>
       <c r="D7" s="1">
         <v>4</v>
       </c>
@@ -2882,10 +2943,10 @@
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="30"/>
+      <c r="C8" s="56"/>
       <c r="D8" s="1">
         <v>1.5</v>
       </c>
@@ -2896,16 +2957,16 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="31" t="s">
+      <c r="C9" s="56"/>
+      <c r="D9" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
@@ -2924,24 +2985,24 @@
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="60" t="s">
+      <c r="A12" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="57" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
       <c r="E13" s="1" t="s">
         <v>114</v>
       </c>
@@ -2974,11 +3035,11 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
+      <c r="B16" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -2990,10 +3051,10 @@
       <c r="C17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" s="1"/>
+      <c r="D17" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="E17" s="46"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
@@ -3039,24 +3100,24 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
+      <c r="B21" s="57" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -3066,7 +3127,7 @@
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -3082,7 +3143,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>24</v>
@@ -3096,14 +3157,14 @@
         <v>1.2490984311009928E-6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
-      <c r="D26" s="70">
+      <c r="D26" s="35">
         <f>((D3/E3)+(D4/E4)+(E14/E5))</f>
         <v>11208083.887880621</v>
       </c>
@@ -3120,44 +3181,44 @@
       <c r="G27" s="2"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="60" t="s">
+      <c r="A28" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="48" t="s">
+      <c r="B28" s="62" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="71" t="s">
         <v>127</v>
       </c>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B29" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
       <c r="E29" s="24"/>
       <c r="F29" s="24"/>
       <c r="G29" s="24"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B30" s="24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C30" s="24" t="s">
         <v>24</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E30" s="22">
         <f>(E25*F18)</f>
         <v>1.3383197476082065E-7</v>
       </c>
       <c r="F30" s="24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G30" s="24"/>
     </row>
@@ -3170,11 +3231,11 @@
       <c r="G31" s="24"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B32" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
+      <c r="B32" s="62" t="s">
+        <v>130</v>
+      </c>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
       <c r="E32" s="24"/>
       <c r="F32" s="24"/>
       <c r="G32" s="24"/>
@@ -3189,13 +3250,13 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C34" s="24" t="s">
         <v>24</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E34" s="24"/>
       <c r="F34" s="24"/>
@@ -3205,7 +3266,7 @@
       <c r="B35" s="24"/>
       <c r="C35" s="24"/>
       <c r="D35" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E35" s="24"/>
       <c r="F35" s="24"/>
@@ -3219,13 +3280,13 @@
         <v>24</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E36" s="24" t="s">
         <v>24</v>
       </c>
       <c r="F36" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G36" s="24"/>
     </row>
@@ -3238,10 +3299,10 @@
       <c r="G37" s="24"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="C38" s="48"/>
+      <c r="B38" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="C38" s="62"/>
       <c r="D38" s="24"/>
       <c r="E38" s="24"/>
       <c r="F38" s="24"/>
@@ -3251,30 +3312,30 @@
       <c r="B39" s="24"/>
       <c r="C39" s="24"/>
       <c r="D39" s="24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E39" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="F39" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="G39" s="48"/>
+      <c r="F39" s="62" t="s">
+        <v>138</v>
+      </c>
+      <c r="G39" s="62"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B40" s="24"/>
       <c r="C40" s="24"/>
       <c r="D40" s="24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E40" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="F40" s="52">
+      <c r="F40" s="70">
         <f>(E30*D3)/E3</f>
         <v>1.2921707907941303E-2</v>
       </c>
-      <c r="G40" s="52"/>
+      <c r="G40" s="70"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="24"/>
@@ -3285,10 +3346,10 @@
       <c r="G41" s="24"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="C42" s="48"/>
+      <c r="B42" s="62" t="s">
+        <v>140</v>
+      </c>
+      <c r="C42" s="62"/>
       <c r="D42" s="24"/>
       <c r="E42" s="24"/>
       <c r="F42" s="24"/>
@@ -3298,30 +3359,30 @@
       <c r="B43" s="24"/>
       <c r="C43" s="24"/>
       <c r="D43" s="24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E43" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="48" t="s">
-        <v>143</v>
-      </c>
-      <c r="G43" s="48"/>
+      <c r="F43" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="G43" s="62"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="24"/>
       <c r="C44" s="24"/>
       <c r="D44" s="24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E44" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="F44" s="52">
+      <c r="F44" s="70">
         <f>(E30*D4)/E4</f>
         <v>1.4870219417868964</v>
       </c>
-      <c r="G44" s="52"/>
+      <c r="G44" s="70"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="24"/>
@@ -3332,10 +3393,10 @@
       <c r="G45" s="24"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B46" s="48" t="s">
-        <v>148</v>
-      </c>
-      <c r="C46" s="48"/>
+      <c r="B46" s="62" t="s">
+        <v>147</v>
+      </c>
+      <c r="C46" s="62"/>
       <c r="D46" s="24"/>
       <c r="E46" s="24"/>
       <c r="F46" s="24"/>
@@ -3345,30 +3406,30 @@
       <c r="B47" s="24"/>
       <c r="C47" s="24"/>
       <c r="D47" s="24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E47" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="F47" s="48" t="s">
-        <v>150</v>
-      </c>
-      <c r="G47" s="48"/>
+      <c r="F47" s="62" t="s">
+        <v>149</v>
+      </c>
+      <c r="G47" s="62"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="24"/>
       <c r="C48" s="24"/>
       <c r="D48" s="24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E48" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="F48" s="52">
+      <c r="F48" s="70">
         <f>(E30*E14)/E5</f>
         <v>5.6350305162450804E-5</v>
       </c>
-      <c r="G48" s="52"/>
+      <c r="G48" s="70"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B49" s="24"/>
@@ -3379,34 +3440,34 @@
       <c r="G49" s="24"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B50" s="48" t="s">
-        <v>144</v>
-      </c>
-      <c r="C50" s="48"/>
-      <c r="D50" s="48"/>
+      <c r="B50" s="62" t="s">
+        <v>143</v>
+      </c>
+      <c r="C50" s="62"/>
+      <c r="D50" s="62"/>
       <c r="E50" s="24"/>
       <c r="F50" s="24"/>
       <c r="G50" s="24"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B51" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D51" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="C51" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="D51" s="24" t="s">
-        <v>147</v>
-      </c>
       <c r="E51" s="24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F51" s="24"/>
       <c r="G51" s="24"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B52" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C52" s="24" t="s">
         <v>24</v>
@@ -3420,73 +3481,199 @@
       <c r="G52" s="24"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B54" s="48"/>
-      <c r="C54" s="48"/>
-      <c r="D54" s="48"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="48"/>
-      <c r="G54" s="48"/>
+      <c r="B54" s="62"/>
+      <c r="C54" s="62"/>
+      <c r="D54" s="62"/>
+      <c r="E54" s="62"/>
+      <c r="F54" s="62"/>
+      <c r="G54" s="62"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B55" s="48"/>
-      <c r="C55" s="48"/>
-      <c r="D55" s="48"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="48"/>
-      <c r="G55" s="48"/>
+      <c r="B55" s="62"/>
+      <c r="C55" s="62"/>
+      <c r="D55" s="62"/>
+      <c r="E55" s="62"/>
+      <c r="F55" s="62"/>
+      <c r="G55" s="62"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B56" s="48"/>
-      <c r="C56" s="48"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="48"/>
+      <c r="B56" s="62"/>
+      <c r="C56" s="62"/>
+      <c r="D56" s="62"/>
+      <c r="E56" s="62"/>
+      <c r="F56" s="62"/>
+      <c r="G56" s="62"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B57" s="48"/>
-      <c r="C57" s="48"/>
-      <c r="D57" s="48"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="48"/>
-      <c r="G57" s="48"/>
+      <c r="B57" s="62"/>
+      <c r="C57" s="62"/>
+      <c r="D57" s="62"/>
+      <c r="E57" s="62"/>
+      <c r="F57" s="62"/>
+      <c r="G57" s="62"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B58" s="48"/>
-      <c r="C58" s="48"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="48"/>
-      <c r="G58" s="48"/>
+      <c r="B58" s="62"/>
+      <c r="C58" s="62"/>
+      <c r="D58" s="62"/>
+      <c r="E58" s="62"/>
+      <c r="F58" s="62"/>
+      <c r="G58" s="62"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B59" s="48"/>
-      <c r="C59" s="48"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
+      <c r="B59" s="62"/>
+      <c r="C59" s="62"/>
+      <c r="D59" s="62"/>
+      <c r="E59" s="62"/>
+      <c r="F59" s="62"/>
+      <c r="G59" s="62"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B60" s="48"/>
-      <c r="C60" s="48"/>
-      <c r="D60" s="48"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
+      <c r="B60" s="62"/>
+      <c r="C60" s="62"/>
+      <c r="D60" s="62"/>
+      <c r="E60" s="62"/>
+      <c r="F60" s="62"/>
+      <c r="G60" s="62"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="3" t="s">
         <v>40</v>
       </c>
+      <c r="B62" s="72" t="s">
+        <v>152</v>
+      </c>
+      <c r="C62" s="72"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="72"/>
+      <c r="F62" s="72"/>
+      <c r="G62" s="72"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B63" s="28"/>
+      <c r="C63" s="28"/>
+      <c r="D63" s="28"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B64" s="73" t="s">
+        <v>157</v>
+      </c>
+      <c r="C64" s="73"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C65" s="1">
+        <v>10</v>
+      </c>
+      <c r="D65" s="1"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="28"/>
+      <c r="G65" s="28"/>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B66" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C66" s="1">
+        <v>80</v>
+      </c>
+      <c r="D66" s="1"/>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B67" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C67" s="57" t="s">
+        <v>158</v>
+      </c>
+      <c r="D67" s="57"/>
+      <c r="E67" s="1">
+        <f>C65*C66</f>
+        <v>800</v>
+      </c>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B68" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="C68" s="57"/>
+      <c r="D68" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E68" s="35">
+        <f>E30*E67</f>
+        <v>1.0706557980865652E-4</v>
+      </c>
+      <c r="F68" s="28"/>
+      <c r="G68" s="28"/>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B69" s="57" t="s">
+        <v>161</v>
+      </c>
+      <c r="C69" s="57"/>
+      <c r="D69" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B70" s="57" t="s">
+        <v>163</v>
+      </c>
+      <c r="C70" s="57"/>
+      <c r="D70" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" s="35">
+        <f>E68*3600</f>
+        <v>0.38543608731116347</v>
+      </c>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B50:D50"/>
+  <mergeCells count="34">
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B54:G60"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B38:C38"/>
@@ -3494,21 +3681,11 @@
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="F43:G43"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B50:D50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
